--- a/shop-main/Dalaila Botique/2023/Format.xlsx
+++ b/shop-main/Dalaila Botique/2023/Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\shop-main\Dalaila Botique\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17C8299-8819-4C82-9731-79AAB2058168}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDCBB50-DD8A-44B7-A2B2-6D297DF75F12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3927,70 +3927,154 @@
       <c r="A21" t="s">
         <v>116</v>
       </c>
+      <c r="B21">
+        <v>601</v>
+      </c>
+      <c r="D21">
+        <v>2010</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>117</v>
       </c>
+      <c r="B22">
+        <v>602</v>
+      </c>
+      <c r="D22">
+        <v>2758</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
+      <c r="B23">
+        <v>603</v>
+      </c>
+      <c r="D23">
+        <v>1662</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
+      <c r="B24">
+        <v>604</v>
+      </c>
+      <c r="D24">
+        <v>1990</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>120</v>
       </c>
+      <c r="B25">
+        <v>605</v>
+      </c>
+      <c r="D25">
+        <v>4249</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>121</v>
       </c>
+      <c r="B26">
+        <v>606</v>
+      </c>
+      <c r="D26">
+        <v>5415</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>122</v>
       </c>
+      <c r="B27">
+        <v>607</v>
+      </c>
+      <c r="D27">
+        <v>2819</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>123</v>
       </c>
+      <c r="B28">
+        <v>608</v>
+      </c>
+      <c r="D28">
+        <v>2776</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>124</v>
       </c>
+      <c r="B29">
+        <v>609</v>
+      </c>
+      <c r="D29">
+        <v>980</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>125</v>
       </c>
+      <c r="B30">
+        <v>610</v>
+      </c>
+      <c r="D30">
+        <v>2540</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>126</v>
       </c>
+      <c r="B31">
+        <v>611</v>
+      </c>
+      <c r="D31">
+        <v>1085</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>127</v>
       </c>
+      <c r="B32">
+        <v>612</v>
+      </c>
+      <c r="D32">
+        <v>2480</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>128</v>
       </c>
+      <c r="B33">
+        <v>613</v>
+      </c>
+      <c r="D33">
+        <v>2345</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>129</v>
+      </c>
+      <c r="B34">
+        <v>614</v>
+      </c>
+      <c r="D34">
+        <v>2835</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="21" x14ac:dyDescent="0.4">
@@ -4001,7 +4085,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="1">
         <f>SUM(D5:D36)</f>
-        <v>49009</v>
+        <v>84953</v>
       </c>
       <c r="E38" s="1">
         <f>SUM(E5:E36)</f>
@@ -4017,7 +4101,7 @@
       <c r="D40" s="13"/>
       <c r="E40" s="6">
         <f>SUM(D38:E38)</f>
-        <v>49009</v>
+        <v>84953</v>
       </c>
     </row>
   </sheetData>
@@ -4086,36 +4170,78 @@
       <c r="A5" t="s">
         <v>130</v>
       </c>
+      <c r="B5">
+        <v>615</v>
+      </c>
+      <c r="D5">
+        <v>3210</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
+      <c r="B6">
+        <v>616</v>
+      </c>
+      <c r="D6">
+        <v>1950</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>132</v>
       </c>
+      <c r="B7">
+        <v>617</v>
+      </c>
+      <c r="D7">
+        <v>2283</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>133</v>
       </c>
+      <c r="B8">
+        <v>618</v>
+      </c>
+      <c r="D8">
+        <v>1900</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>134</v>
       </c>
+      <c r="B9">
+        <v>619</v>
+      </c>
+      <c r="D9">
+        <v>1100</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>135</v>
       </c>
+      <c r="B10">
+        <v>620</v>
+      </c>
+      <c r="D10">
+        <v>2685</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>136</v>
       </c>
+      <c r="B11">
+        <v>621</v>
+      </c>
+      <c r="D11">
+        <v>3354</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -4126,98 +4252,176 @@
       <c r="A13" t="s">
         <v>138</v>
       </c>
+      <c r="B13">
+        <v>622</v>
+      </c>
+      <c r="D13">
+        <v>4670</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>139</v>
       </c>
+      <c r="B14">
+        <v>623</v>
+      </c>
+      <c r="D14">
+        <v>690</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>140</v>
       </c>
+      <c r="B15">
+        <v>624</v>
+      </c>
+      <c r="D15">
+        <v>2391</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>625</v>
+      </c>
+      <c r="D16">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>626</v>
+      </c>
+      <c r="D17">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>627</v>
+      </c>
+      <c r="D18">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>628</v>
+      </c>
+      <c r="D20">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>629</v>
+      </c>
+      <c r="D21">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>630</v>
+      </c>
+      <c r="D22">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>631</v>
+      </c>
+      <c r="D24">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>632</v>
+      </c>
+      <c r="D25">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>633</v>
+      </c>
+      <c r="D26">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>634</v>
+      </c>
+      <c r="D27">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>157</v>
       </c>
@@ -4245,7 +4449,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="1">
         <f>SUM(D5:D36)</f>
-        <v>0</v>
+        <v>46545</v>
       </c>
       <c r="E38" s="1">
         <f>SUM(E5:E36)</f>
@@ -4261,7 +4465,7 @@
       <c r="D40" s="13"/>
       <c r="E40" s="6">
         <f>SUM(D38:E38)</f>
-        <v>0</v>
+        <v>46545</v>
       </c>
     </row>
   </sheetData>
